--- a/nextseek_api/batch_upload/tests/fixtures/wave3_update_mode.xlsx
+++ b/nextseek_api/batch_upload/tests/fixtures/wave3_update_mode.xlsx
@@ -449,18 +449,26 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WTNAM-240301BMC-1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>W3NHP_blood</t>
+          <t>WTNAM_blood</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"Name": "drift-a", "Scientist": "Updated Scientist"}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>{"UID":"WTNAM-240301BMC-1","Name":"drift-a","Scientist":"Updated Scientist"}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
       <c r="E2" t="n">
         <v>701</v>
       </c>
@@ -471,18 +479,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D.WTFIL-240301BMC-1</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D.W3IT_files</t>
+          <t>D.WTFIL_files</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"File_PrimartyData": "drift-d.fastq", "Scientist": "Updated File Scientist"}</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>{"UID":"D.WTFIL-240301BMC-1","File_PrimartyData":"drift-d.fastq","Scientist":"Updated File Scientist"}</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
       <c r="E3" t="n">
         <v>701</v>
       </c>
@@ -495,20 +511,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W3IT-240301NA-5</t>
+          <t>WTNAM-240301BMC-5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>W3NHP_blood</t>
+          <t>WTNAM_blood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"UID": "W3IT-240301NA-5", "Scientist": "UID Only Update"}</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>{"UID":"WTNAM-240301BMC-5","Scientist":"UID Only Update"}</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>701</v>
       </c>
@@ -519,18 +539,21 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>W3NHP_blood</t>
+          <t>WTNAM_blood</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"Name": "child-ambiguous-update", "Parent": "dup"}</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>{"UID":null,"Name":"child-ambiguous-update","Parent":"dup"}</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
       <c r="E5" t="n">
         <v>701</v>
       </c>
@@ -541,18 +564,21 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>W3NHP_blood</t>
+          <t>WTNAM_blood</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"Name": "future-parent"}</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>{"UID":null,"Name":"future-parent"}</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
       <c r="E6" t="n">
         <v>701</v>
       </c>

--- a/nextseek_api/batch_upload/tests/fixtures/wave3_update_mode.xlsx
+++ b/nextseek_api/batch_upload/tests/fixtures/wave3_update_mode.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"UID":null,"Name":"future-parent"}</t>
+          <t>{"UID":null,"Name":"child-of-oversized","Parent":"GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_1_S13_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_2_S14_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_3_S15_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_4_S16_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_5_S17_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_6_S18_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_7_S19_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_8_S20_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_9_S21_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_10_S22_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_11_S23_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_12_S24_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_13_S25_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_14_S26_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_15_S27_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_16_S28_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_17_S29_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_18_S30_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_19_S31_L001_I1_001.fastq.gz; GBM1-DFCI4-S1to6-CSFCells-1_VDJ_IGO_16516_B_20_S32_L001_I1_001.fastq.gz"}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -583,6 +583,31 @@
         <v>701</v>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>Wave 3 Integration Study</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WTNAM_blood</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{"UID":null,"Name":"future-parent"}</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>701</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Wave 3 Integration Study</t>
         </is>
